--- a/data/empresas/Pacifico Cable SpA/temp_uploaded.xlsx
+++ b/data/empresas/Pacifico Cable SpA/temp_uploaded.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mundo\2026\Agosto 2026\Pacifico\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Mundo\Programa de informes\Test de carga Pacifico\Agosto 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{143020D4-0C6F-4106-B526-FF4D4C79D2D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{265CC481-94AB-4315-9705-D2BFB5369AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{026CEAF2-3E5F-4B59-A6F9-2B4C84154F40}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{C86984FD-1177-4807-84E1-F87F749FEE4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="377">
   <si>
     <t>N° de Cuenta</t>
   </si>
@@ -62,16 +62,16 @@
     <t>BANCO BCI CL</t>
   </si>
   <si>
-    <t>BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>BANCO SCOTIABANK USD</t>
+    <t xml:space="preserve">BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BANCO SCOTIABANK USD </t>
   </si>
   <si>
     <t>ABONOS BANCO BCI CL</t>
@@ -80,28 +80,28 @@
     <t>CARGOS BANCO BCI CL</t>
   </si>
   <si>
-    <t>ABONOS BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO BCI USD</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO BCI EUR</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO SCOTIABANK CL</t>
-  </si>
-  <si>
-    <t>ABONOS BANCO SCOTIABANK USD</t>
-  </si>
-  <si>
-    <t>CARGOS BANCO SCOTIABANK USD</t>
+    <t xml:space="preserve">ABONOS BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO BCI USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO BCI EUR </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO SCOTIABANK CL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABONOS BANCO SCOTIABANK USD </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CARGOS BANCO SCOTIABANK USD </t>
   </si>
   <si>
     <t>CUENTA TRANSFERENCIA INTERNA</t>
@@ -254,7 +254,7 @@
     <t>ANTICIPO PROVEEDORES EXTRANJEROS</t>
   </si>
   <si>
-    <t>GASTOS ANTICIPADOS</t>
+    <t xml:space="preserve">GASTOS ANTICIPADOS </t>
   </si>
   <si>
     <t>ANTICIPO ARRIENDOS</t>
@@ -266,13 +266,15 @@
     <t>ANTICIPO PROVEEDORES EXTRANJEROS USD</t>
   </si>
   <si>
-    <t>CUENTAS POR COBRAR CONTRATISTAS</t>
+    <t xml:space="preserve">CUENTAS POR COBRAR CONTRATISTAS 
+</t>
   </si>
   <si>
     <t>OTROS DEUDORES</t>
   </si>
   <si>
-    <t>ANTICIPO PROVEEDORES EXTRANJEROS YUAN</t>
+    <t xml:space="preserve">ANTICIPO PROVEEDORES EXTRANJEROS YUAN 
+</t>
   </si>
   <si>
     <t>MERCADERIA EN TRANSITO USD</t>
@@ -302,7 +304,7 @@
     <t>MATERIALES NACIONALES</t>
   </si>
   <si>
-    <t>MATERIALES NACIONALES DETERIORADOS</t>
+    <t xml:space="preserve">MATERIALES NACIONALES DETERIORADOS			</t>
   </si>
   <si>
     <t>ROPA DE TRABAJO Y MATERIALES DE SEGURIDAD</t>
@@ -353,7 +355,7 @@
     <t>REPUESTOS</t>
   </si>
   <si>
-    <t>AJUSTES INVENTARIOS BODEGAS</t>
+    <t xml:space="preserve">AJUSTES INVENTARIOS BODEGAS </t>
   </si>
   <si>
     <t>INVENTARIO CRM</t>
@@ -434,7 +436,7 @@
     <t>EQUIPOS SERIADOS</t>
   </si>
   <si>
-    <t>MATERIALES DOMICILIARIOS</t>
+    <t xml:space="preserve">MATERIALES DOMICILIARIOS </t>
   </si>
   <si>
     <t>DETERIORO MUEBLES, EQUIPOS MENORES</t>
@@ -470,22 +472,22 @@
     <t>DEPRECIACION ACUMULADA CONSTRUCCIONES Y OBRAS</t>
   </si>
   <si>
-    <t>DEPRECIACION ACUMULADA REDES DE TRANSMISION</t>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA REDES DE TRANSMISION			</t>
   </si>
   <si>
     <t>DEPRECIACION ACUMULADA EQUIPOS COMPUTACIONALES</t>
   </si>
   <si>
-    <t>DEPRECIACION ACUMULADA MUEBLES Y UTILES</t>
-  </si>
-  <si>
-    <t>DEPRECIACION ACUMULADA VEHICULOS</t>
-  </si>
-  <si>
-    <t>DEPRECIACION ACUMULADA OTROS ACTIVOS FIJOS</t>
-  </si>
-  <si>
-    <t>DEPRECIACION ACUMULADA ACTIVOS EN ARRENDAMIENTO</t>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA MUEBLES Y UTILES			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA VEHICULOS			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA OTROS ACTIVOS FIJOS			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEPRECIACION ACUMULADA ACTIVOS EN ARRENDAMIENTO			</t>
   </si>
   <si>
     <t>DEPRECIACION ACUMULADA PLANTA TRANSMISORA</t>
@@ -581,7 +583,7 @@
     <t>PROVISIONES VARIAS</t>
   </si>
   <si>
-    <t>PROVISIONES SEÑALES</t>
+    <t xml:space="preserve">PROVISIONES SEÑALES			</t>
   </si>
   <si>
     <t>PROVISION DE COSTO</t>
@@ -719,7 +721,7 @@
     <t>AJUSTE DEVENGO INGRESOS MOVIL</t>
   </si>
   <si>
-    <t>INGRESOS ARRIENDO FIBRA OPTICA</t>
+    <t>INGRESOS ARRIENDO FIBRA OPTICA </t>
   </si>
   <si>
     <t>INGRESOS TELEFONIA CARGOS DE ACCESO FIJO</t>
@@ -761,13 +763,13 @@
     <t>DIRECCIONES IP</t>
   </si>
   <si>
-    <t>TRAMAS</t>
-  </si>
-  <si>
-    <t>TRANSITO</t>
-  </si>
-  <si>
-    <t>PORTABILIDAD</t>
+    <t xml:space="preserve">TRAMAS			</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRANSITO	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PORTABILIDAD	</t>
   </si>
   <si>
     <t>COSTOS CARGOS DE ACCESO FIJO</t>
@@ -950,7 +952,7 @@
     <t>MULTAS E INTERESES</t>
   </si>
   <si>
-    <t>SEGUROS, INMUEBLES Y OTROS</t>
+    <t xml:space="preserve">SEGUROS, INMUEBLES Y OTROS			</t>
   </si>
   <si>
     <t>GASTO MANTENCION PROPIEDADES</t>
@@ -959,7 +961,7 @@
     <t>GASTO MANTENCION Y REPARACION EQUIPOS</t>
   </si>
   <si>
-    <t>MATERIALES</t>
+    <t xml:space="preserve">MATERIALES </t>
   </si>
   <si>
     <t>INSUMOS (RESULTADO)</t>
@@ -1170,9 +1172,6 @@
   </si>
   <si>
     <t>IMPUESTO A LA RENTA (DIFERIDO)</t>
-  </si>
-  <si>
-    <t>CUENTA PUENTE CARGA INICIAL</t>
   </si>
 </sst>
 </file>
@@ -1596,13 +1595,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B7A3438-3952-4265-9755-B3F0B42764CF}">
-  <dimension ref="A1:C377"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9F9B33-B3DB-480B-BE0B-B04CD502010E}">
+  <dimension ref="A1:C376"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="61.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2580,7 +2575,7 @@
         <v>90</v>
       </c>
       <c r="C89" s="4">
-        <v>9215805989</v>
+        <v>9205523501</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -2624,7 +2619,7 @@
         <v>94</v>
       </c>
       <c r="C93" s="4">
-        <v>3040006598</v>
+        <v>3038061878</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.3">
@@ -3119,7 +3114,7 @@
         <v>139</v>
       </c>
       <c r="C138" s="4">
-        <v>-3240803916</v>
+        <v>-2589090938</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -3405,7 +3400,7 @@
         <v>165</v>
       </c>
       <c r="C164" s="4">
-        <v>-10485622901</v>
+        <v>-11125108671</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.3">
@@ -4802,7 +4797,7 @@
         <v>291</v>
       </c>
       <c r="C291" s="4">
-        <v>52816866115</v>
+        <v>52822795073</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
@@ -4813,7 +4808,7 @@
         <v>292</v>
       </c>
       <c r="C292" s="4">
-        <v>1349457156</v>
+        <v>1343528198</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -5740,19 +5735,7 @@
         <v>-8206251324</v>
       </c>
     </row>
-    <row r="377" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A377" s="7">
-        <v>9999999</v>
-      </c>
-      <c r="B377" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="C377" s="4">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>